--- a/Tabelas/casos_por_governo.xlsx
+++ b/Tabelas/casos_por_governo.xlsx
@@ -458,7 +458,7 @@
         <v>1875</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         <v>3150</v>
       </c>
       <c r="D3" t="n">
-        <v>54.26</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>780</v>
+        <v>1123</v>
       </c>
       <c r="D4" t="n">
-        <v>13.44</v>
+        <v>18.27</v>
       </c>
     </row>
   </sheetData>
